--- a/download/Suivi_Hebdomadaire_Gharb_2026.xlsx
+++ b/download/Suivi_Hebdomadaire_Gharb_2026.xlsx
@@ -171,7 +171,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -198,11 +198,20 @@
         <color rgb="00BDBDBD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000D47A1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -369,6 +378,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -765,6 +778,7 @@
   <sheetPr>
     <tabColor rgb="002E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:U78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -794,7 +808,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SUIVI HEBDOMADAIRE D'EXÉCUTION PHYSIQUE ET FINANCIÈRE — PROJETS INONDATIONS GHARB 2026</t>
+          <t>SUIVI HEBDOMADAIRE D'EXÉCUTION PHYSIQUE ET FINANCIÈRE — PROJETS INONDATIONS GHARB 2026 (Juin–Décembre)</t>
         </is>
       </c>
     </row>
@@ -816,12 +830,12 @@
         </is>
       </c>
       <c r="O3" s="6" t="n"/>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="64" t="inlineStr">
         <is>
           <t>Date fin :</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="n"/>
+      <c r="Q3" s="65" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="B5" s="7" t="inlineStr">
@@ -5665,8 +5679,8 @@
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="L3:N3"/>
     <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="L3:N3"/>
   </mergeCells>
   <conditionalFormatting sqref="K6:K77">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
@@ -5760,14 +5774,14 @@
     <row r="2" ht="35" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>HISTORIQUE D'AVANCEMENT PAR SEMAINE — VUE D'ENSEMBLE</t>
+          <t>HISTORIQUE D'AVANCEMENT PAR SEMAINE — VUE D'ENSEMBLE (Juin–Décembre 2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>Ce tableau permet de suivre l'évolution semaine par semaine de l'avancement global par province</t>
+          <t>Ce tableau permet de suivre l'évolution semaine par semaine de l'avancement global par province (Juin à Décembre 2026)</t>
         </is>
       </c>
     </row>
@@ -5826,9 +5840,13 @@
     </row>
     <row r="6">
       <c r="B6" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="34" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>01/06/2026 - 07/06/2026</t>
+        </is>
+      </c>
       <c r="D6" s="35" t="n"/>
       <c r="E6" s="12" t="n"/>
       <c r="F6" s="12" t="n"/>
@@ -5841,9 +5859,13 @@
     </row>
     <row r="7">
       <c r="B7" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="34" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>08/06/2026 - 14/06/2026</t>
+        </is>
+      </c>
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="12" t="n"/>
       <c r="F7" s="12" t="n"/>
@@ -5856,9 +5878,13 @@
     </row>
     <row r="8">
       <c r="B8" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="34" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>15/06/2026 - 21/06/2026</t>
+        </is>
+      </c>
       <c r="D8" s="35" t="n"/>
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="12" t="n"/>
@@ -5871,9 +5897,13 @@
     </row>
     <row r="9">
       <c r="B9" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="34" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>22/06/2026 - 28/06/2026</t>
+        </is>
+      </c>
       <c r="D9" s="37" t="n"/>
       <c r="E9" s="12" t="n"/>
       <c r="F9" s="12" t="n"/>
@@ -5886,9 +5916,13 @@
     </row>
     <row r="10">
       <c r="B10" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="34" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>29/06/2026 - 05/07/2026</t>
+        </is>
+      </c>
       <c r="D10" s="35" t="n"/>
       <c r="E10" s="12" t="n"/>
       <c r="F10" s="12" t="n"/>
@@ -5901,9 +5935,13 @@
     </row>
     <row r="11">
       <c r="B11" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="34" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>06/07/2026 - 12/07/2026</t>
+        </is>
+      </c>
       <c r="D11" s="37" t="n"/>
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="12" t="n"/>
@@ -5916,9 +5954,13 @@
     </row>
     <row r="12">
       <c r="B12" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="34" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>13/07/2026 - 19/07/2026</t>
+        </is>
+      </c>
       <c r="D12" s="35" t="n"/>
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
@@ -5931,9 +5973,13 @@
     </row>
     <row r="13">
       <c r="B13" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="34" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>20/07/2026 - 26/07/2026</t>
+        </is>
+      </c>
       <c r="D13" s="37" t="n"/>
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="12" t="n"/>
@@ -5946,9 +5992,13 @@
     </row>
     <row r="14">
       <c r="B14" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="34" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>27/07/2026 - 02/08/2026</t>
+        </is>
+      </c>
       <c r="D14" s="35" t="n"/>
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="12" t="n"/>
@@ -5961,9 +6011,13 @@
     </row>
     <row r="15">
       <c r="B15" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="34" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>03/08/2026 - 09/08/2026</t>
+        </is>
+      </c>
       <c r="D15" s="37" t="n"/>
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="12" t="n"/>
@@ -5976,9 +6030,13 @@
     </row>
     <row r="16">
       <c r="B16" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" s="34" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>10/08/2026 - 16/08/2026</t>
+        </is>
+      </c>
       <c r="D16" s="35" t="n"/>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
@@ -5991,9 +6049,13 @@
     </row>
     <row r="17">
       <c r="B17" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" s="34" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>17/08/2026 - 23/08/2026</t>
+        </is>
+      </c>
       <c r="D17" s="37" t="n"/>
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="12" t="n"/>
@@ -6006,9 +6068,13 @@
     </row>
     <row r="18">
       <c r="B18" s="33" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" s="34" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>24/08/2026 - 30/08/2026</t>
+        </is>
+      </c>
       <c r="D18" s="35" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="12" t="n"/>
@@ -6021,9 +6087,13 @@
     </row>
     <row r="19">
       <c r="B19" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" s="34" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>31/08/2026 - 06/09/2026</t>
+        </is>
+      </c>
       <c r="D19" s="37" t="n"/>
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="12" t="n"/>
@@ -6036,9 +6106,13 @@
     </row>
     <row r="20">
       <c r="B20" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" s="34" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>07/09/2026 - 13/09/2026</t>
+        </is>
+      </c>
       <c r="D20" s="35" t="n"/>
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="12" t="n"/>
@@ -6051,9 +6125,13 @@
     </row>
     <row r="21">
       <c r="B21" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="C21" s="34" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>14/09/2026 - 20/09/2026</t>
+        </is>
+      </c>
       <c r="D21" s="37" t="n"/>
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
@@ -6066,9 +6144,13 @@
     </row>
     <row r="22">
       <c r="B22" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="C22" s="34" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>21/09/2026 - 27/09/2026</t>
+        </is>
+      </c>
       <c r="D22" s="35" t="n"/>
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="12" t="n"/>
@@ -6081,9 +6163,13 @@
     </row>
     <row r="23">
       <c r="B23" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="C23" s="34" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>28/09/2026 - 04/10/2026</t>
+        </is>
+      </c>
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="12" t="n"/>
@@ -6096,9 +6182,13 @@
     </row>
     <row r="24">
       <c r="B24" s="33" t="n">
-        <v>19</v>
-      </c>
-      <c r="C24" s="34" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>05/10/2026 - 11/10/2026</t>
+        </is>
+      </c>
       <c r="D24" s="35" t="n"/>
       <c r="E24" s="12" t="n"/>
       <c r="F24" s="12" t="n"/>
@@ -6111,9 +6201,13 @@
     </row>
     <row r="25">
       <c r="B25" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="C25" s="34" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>12/10/2026 - 18/10/2026</t>
+        </is>
+      </c>
       <c r="D25" s="37" t="n"/>
       <c r="E25" s="12" t="n"/>
       <c r="F25" s="12" t="n"/>
@@ -6126,9 +6220,13 @@
     </row>
     <row r="26">
       <c r="B26" s="33" t="n">
-        <v>21</v>
-      </c>
-      <c r="C26" s="34" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>19/10/2026 - 25/10/2026</t>
+        </is>
+      </c>
       <c r="D26" s="35" t="n"/>
       <c r="E26" s="12" t="n"/>
       <c r="F26" s="12" t="n"/>
@@ -6141,9 +6239,13 @@
     </row>
     <row r="27">
       <c r="B27" s="36" t="n">
-        <v>22</v>
-      </c>
-      <c r="C27" s="34" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>26/10/2026 - 01/11/2026</t>
+        </is>
+      </c>
       <c r="D27" s="37" t="n"/>
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="12" t="n"/>
@@ -6156,9 +6258,13 @@
     </row>
     <row r="28">
       <c r="B28" s="33" t="n">
-        <v>23</v>
-      </c>
-      <c r="C28" s="34" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>02/11/2026 - 08/11/2026</t>
+        </is>
+      </c>
       <c r="D28" s="35" t="n"/>
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
@@ -6171,9 +6277,13 @@
     </row>
     <row r="29">
       <c r="B29" s="36" t="n">
-        <v>24</v>
-      </c>
-      <c r="C29" s="34" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>09/11/2026 - 15/11/2026</t>
+        </is>
+      </c>
       <c r="D29" s="37" t="n"/>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="12" t="n"/>
@@ -6186,9 +6296,13 @@
     </row>
     <row r="30">
       <c r="B30" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="C30" s="34" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>16/11/2026 - 22/11/2026</t>
+        </is>
+      </c>
       <c r="D30" s="35" t="n"/>
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="12" t="n"/>
@@ -6201,9 +6315,13 @@
     </row>
     <row r="31">
       <c r="B31" s="36" t="n">
-        <v>26</v>
-      </c>
-      <c r="C31" s="34" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>23/11/2026 - 29/11/2026</t>
+        </is>
+      </c>
       <c r="D31" s="37" t="n"/>
       <c r="E31" s="12" t="n"/>
       <c r="F31" s="12" t="n"/>
@@ -6216,9 +6334,13 @@
     </row>
     <row r="32">
       <c r="B32" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="C32" s="34" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>30/11/2026 - 06/12/2026</t>
+        </is>
+      </c>
       <c r="D32" s="35" t="n"/>
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="12" t="n"/>
@@ -6231,9 +6353,13 @@
     </row>
     <row r="33">
       <c r="B33" s="36" t="n">
-        <v>28</v>
-      </c>
-      <c r="C33" s="34" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>07/12/2026 - 13/12/2026</t>
+        </is>
+      </c>
       <c r="D33" s="37" t="n"/>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
@@ -6246,9 +6372,13 @@
     </row>
     <row r="34">
       <c r="B34" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="C34" s="34" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>14/12/2026 - 20/12/2026</t>
+        </is>
+      </c>
       <c r="D34" s="35" t="n"/>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="12" t="n"/>
@@ -6261,9 +6391,13 @@
     </row>
     <row r="35">
       <c r="B35" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="C35" s="34" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>21/12/2026 - 27/12/2026</t>
+        </is>
+      </c>
       <c r="D35" s="37" t="n"/>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="12" t="n"/>
@@ -6276,9 +6410,13 @@
     </row>
     <row r="36">
       <c r="B36" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="C36" s="34" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>28/12/2026 - 03/01/2027</t>
+        </is>
+      </c>
       <c r="D36" s="35" t="n"/>
       <c r="E36" s="12" t="n"/>
       <c r="F36" s="12" t="n"/>
@@ -6290,9 +6428,7 @@
       <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="36" t="n">
-        <v>32</v>
-      </c>
+      <c r="B37" s="36" t="n"/>
       <c r="C37" s="34" t="n"/>
       <c r="D37" s="37" t="n"/>
       <c r="E37" s="12" t="n"/>
@@ -6305,9 +6441,7 @@
       <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="33" t="n">
-        <v>33</v>
-      </c>
+      <c r="B38" s="33" t="n"/>
       <c r="C38" s="34" t="n"/>
       <c r="D38" s="35" t="n"/>
       <c r="E38" s="12" t="n"/>
@@ -6320,9 +6454,7 @@
       <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="36" t="n">
-        <v>34</v>
-      </c>
+      <c r="B39" s="36" t="n"/>
       <c r="C39" s="34" t="n"/>
       <c r="D39" s="37" t="n"/>
       <c r="E39" s="12" t="n"/>
@@ -6335,9 +6467,7 @@
       <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="33" t="n">
-        <v>35</v>
-      </c>
+      <c r="B40" s="33" t="n"/>
       <c r="C40" s="34" t="n"/>
       <c r="D40" s="35" t="n"/>
       <c r="E40" s="12" t="n"/>
@@ -6350,9 +6480,7 @@
       <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="36" t="n">
-        <v>36</v>
-      </c>
+      <c r="B41" s="36" t="n"/>
       <c r="C41" s="34" t="n"/>
       <c r="D41" s="37" t="n"/>
       <c r="E41" s="12" t="n"/>
@@ -6365,9 +6493,7 @@
       <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="33" t="n">
-        <v>37</v>
-      </c>
+      <c r="B42" s="33" t="n"/>
       <c r="C42" s="34" t="n"/>
       <c r="D42" s="35" t="n"/>
       <c r="E42" s="12" t="n"/>
@@ -6380,9 +6506,7 @@
       <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="36" t="n">
-        <v>38</v>
-      </c>
+      <c r="B43" s="36" t="n"/>
       <c r="C43" s="34" t="n"/>
       <c r="D43" s="37" t="n"/>
       <c r="E43" s="12" t="n"/>
@@ -6395,9 +6519,7 @@
       <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="33" t="n">
-        <v>39</v>
-      </c>
+      <c r="B44" s="33" t="n"/>
       <c r="C44" s="34" t="n"/>
       <c r="D44" s="35" t="n"/>
       <c r="E44" s="12" t="n"/>
@@ -6410,9 +6532,7 @@
       <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="36" t="n">
-        <v>40</v>
-      </c>
+      <c r="B45" s="36" t="n"/>
       <c r="C45" s="34" t="n"/>
       <c r="D45" s="37" t="n"/>
       <c r="E45" s="12" t="n"/>
@@ -6425,9 +6545,7 @@
       <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="33" t="n">
-        <v>41</v>
-      </c>
+      <c r="B46" s="33" t="n"/>
       <c r="C46" s="34" t="n"/>
       <c r="D46" s="35" t="n"/>
       <c r="E46" s="12" t="n"/>
@@ -6440,9 +6558,7 @@
       <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="36" t="n">
-        <v>42</v>
-      </c>
+      <c r="B47" s="36" t="n"/>
       <c r="C47" s="34" t="n"/>
       <c r="D47" s="37" t="n"/>
       <c r="E47" s="12" t="n"/>
@@ -6455,9 +6571,7 @@
       <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="33" t="n">
-        <v>43</v>
-      </c>
+      <c r="B48" s="33" t="n"/>
       <c r="C48" s="34" t="n"/>
       <c r="D48" s="35" t="n"/>
       <c r="E48" s="12" t="n"/>
@@ -6470,9 +6584,7 @@
       <c r="L48" s="12" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="36" t="n">
-        <v>44</v>
-      </c>
+      <c r="B49" s="36" t="n"/>
       <c r="C49" s="34" t="n"/>
       <c r="D49" s="37" t="n"/>
       <c r="E49" s="12" t="n"/>
@@ -6485,9 +6597,7 @@
       <c r="L49" s="12" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="33" t="n">
-        <v>45</v>
-      </c>
+      <c r="B50" s="33" t="n"/>
       <c r="C50" s="34" t="n"/>
       <c r="D50" s="35" t="n"/>
       <c r="E50" s="12" t="n"/>
@@ -6500,9 +6610,7 @@
       <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="36" t="n">
-        <v>46</v>
-      </c>
+      <c r="B51" s="36" t="n"/>
       <c r="C51" s="34" t="n"/>
       <c r="D51" s="37" t="n"/>
       <c r="E51" s="12" t="n"/>
@@ -6515,9 +6623,7 @@
       <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="33" t="n">
-        <v>47</v>
-      </c>
+      <c r="B52" s="33" t="n"/>
       <c r="C52" s="34" t="n"/>
       <c r="D52" s="35" t="n"/>
       <c r="E52" s="12" t="n"/>
@@ -6530,9 +6636,7 @@
       <c r="L52" s="12" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="36" t="n">
-        <v>48</v>
-      </c>
+      <c r="B53" s="36" t="n"/>
       <c r="C53" s="34" t="n"/>
       <c r="D53" s="37" t="n"/>
       <c r="E53" s="12" t="n"/>
@@ -6545,9 +6649,7 @@
       <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="33" t="n">
-        <v>49</v>
-      </c>
+      <c r="B54" s="33" t="n"/>
       <c r="C54" s="34" t="n"/>
       <c r="D54" s="35" t="n"/>
       <c r="E54" s="12" t="n"/>
@@ -6560,9 +6662,7 @@
       <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="36" t="n">
-        <v>50</v>
-      </c>
+      <c r="B55" s="36" t="n"/>
       <c r="C55" s="34" t="n"/>
       <c r="D55" s="37" t="n"/>
       <c r="E55" s="12" t="n"/>
@@ -6575,9 +6675,7 @@
       <c r="L55" s="12" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="33" t="n">
-        <v>51</v>
-      </c>
+      <c r="B56" s="33" t="n"/>
       <c r="C56" s="34" t="n"/>
       <c r="D56" s="35" t="n"/>
       <c r="E56" s="12" t="n"/>
@@ -6590,9 +6688,7 @@
       <c r="L56" s="12" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="36" t="n">
-        <v>52</v>
-      </c>
+      <c r="B57" s="36" t="n"/>
       <c r="C57" s="34" t="n"/>
       <c r="D57" s="37" t="n"/>
       <c r="E57" s="12" t="n"/>
@@ -6638,7 +6734,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="B2" s="38" t="inlineStr">
         <is>
-          <t>RÉCAPITULATIF PAR PROVINCE — SEMAINE EN COURS</t>
+          <t>RÉCAPITULATIF PAR PROVINCE — SEMAINE EN COURS (Juin–Décembre 2026)</t>
         </is>
       </c>
     </row>
@@ -6881,13 +6977,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="35" customHeight="1">
       <c r="B2" s="60" t="inlineStr">
         <is>
@@ -6895,6 +6992,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="61" t="inlineStr">
         <is>
@@ -6903,10 +7001,11 @@
       </c>
       <c r="C4" s="62" t="inlineStr">
         <is>
-          <t>Ce fichier permet d'assurer un suivi hebdomadaire de l'exécution physique et financière des 72 projets de lutte contre les inondations dans la région du Gharb.</t>
-        </is>
-      </c>
-    </row>
+          <t>Ce fichier permet d'assurer un suivi hebdomadaire (Juin à Décembre 2026) de l'exécution physique et financière des 72 projets de lutte contre les inondations dans la région du Gharb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="63" t="inlineStr">
         <is>
@@ -6965,6 +7064,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="63" t="inlineStr">
         <is>
@@ -7002,6 +7102,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="63" t="inlineStr">
         <is>
@@ -7026,6 +7127,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="63" t="inlineStr">
         <is>
@@ -7117,6 +7219,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="63" t="inlineStr">
         <is>

--- a/download/Suivi_Hebdomadaire_Gharb_2026.xlsx
+++ b/download/Suivi_Hebdomadaire_Gharb_2026.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="+0.0;-0.0;0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +112,14 @@
       <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -170,8 +176,20 @@
         <fgColor rgb="00757575"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -207,11 +225,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -382,6 +406,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -780,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:U78"/>
+  <dimension ref="B2:AB78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="2" max="2"/>
@@ -938,6 +968,41 @@
           <t>Observations</t>
         </is>
       </c>
+      <c r="V5" s="66" t="inlineStr">
+        <is>
+          <t>N° Consultation</t>
+        </is>
+      </c>
+      <c r="W5" s="66" t="inlineStr">
+        <is>
+          <t>Société Titulaire</t>
+        </is>
+      </c>
+      <c r="X5" s="66" t="inlineStr">
+        <is>
+          <t>Date Ouverture Plis</t>
+        </is>
+      </c>
+      <c r="Y5" s="66" t="inlineStr">
+        <is>
+          <t>Date Jugement</t>
+        </is>
+      </c>
+      <c r="Z5" s="66" t="inlineStr">
+        <is>
+          <t>Date OSC</t>
+        </is>
+      </c>
+      <c r="AA5" s="66" t="inlineStr">
+        <is>
+          <t>Délai Exécution (j)</t>
+        </is>
+      </c>
+      <c r="AB5" s="66" t="inlineStr">
+        <is>
+          <t>Date Réception Provisoire</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="8" t="n">
@@ -1003,6 +1068,13 @@
       </c>
       <c r="T6" s="16" t="n"/>
       <c r="U6" s="17" t="n"/>
+      <c r="V6" s="67" t="n"/>
+      <c r="W6" s="67" t="n"/>
+      <c r="X6" s="67" t="n"/>
+      <c r="Y6" s="67" t="n"/>
+      <c r="Z6" s="67" t="n"/>
+      <c r="AA6" s="67" t="n"/>
+      <c r="AB6" s="67" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" s="18" t="n">
@@ -1068,6 +1140,13 @@
       </c>
       <c r="T7" s="16" t="n"/>
       <c r="U7" s="17" t="n"/>
+      <c r="V7" s="67" t="n"/>
+      <c r="W7" s="67" t="n"/>
+      <c r="X7" s="67" t="n"/>
+      <c r="Y7" s="67" t="n"/>
+      <c r="Z7" s="67" t="n"/>
+      <c r="AA7" s="67" t="n"/>
+      <c r="AB7" s="67" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="B8" s="8" t="n">
@@ -1133,6 +1212,13 @@
       </c>
       <c r="T8" s="16" t="n"/>
       <c r="U8" s="17" t="n"/>
+      <c r="V8" s="67" t="n"/>
+      <c r="W8" s="67" t="n"/>
+      <c r="X8" s="67" t="n"/>
+      <c r="Y8" s="67" t="n"/>
+      <c r="Z8" s="67" t="n"/>
+      <c r="AA8" s="67" t="n"/>
+      <c r="AB8" s="67" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="B9" s="18" t="n">
@@ -1198,6 +1284,13 @@
       </c>
       <c r="T9" s="16" t="n"/>
       <c r="U9" s="17" t="n"/>
+      <c r="V9" s="67" t="n"/>
+      <c r="W9" s="67" t="n"/>
+      <c r="X9" s="67" t="n"/>
+      <c r="Y9" s="67" t="n"/>
+      <c r="Z9" s="67" t="n"/>
+      <c r="AA9" s="67" t="n"/>
+      <c r="AB9" s="67" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="B10" s="8" t="n">
@@ -1263,6 +1356,13 @@
       </c>
       <c r="T10" s="16" t="n"/>
       <c r="U10" s="17" t="n"/>
+      <c r="V10" s="67" t="n"/>
+      <c r="W10" s="67" t="n"/>
+      <c r="X10" s="67" t="n"/>
+      <c r="Y10" s="67" t="n"/>
+      <c r="Z10" s="67" t="n"/>
+      <c r="AA10" s="67" t="n"/>
+      <c r="AB10" s="67" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="B11" s="18" t="n">
@@ -1324,6 +1424,13 @@
       </c>
       <c r="T11" s="16" t="n"/>
       <c r="U11" s="17" t="n"/>
+      <c r="V11" s="67" t="n"/>
+      <c r="W11" s="67" t="n"/>
+      <c r="X11" s="67" t="n"/>
+      <c r="Y11" s="67" t="n"/>
+      <c r="Z11" s="67" t="n"/>
+      <c r="AA11" s="67" t="n"/>
+      <c r="AB11" s="67" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="B12" s="8" t="n">
@@ -1389,6 +1496,13 @@
       </c>
       <c r="T12" s="16" t="n"/>
       <c r="U12" s="17" t="n"/>
+      <c r="V12" s="67" t="n"/>
+      <c r="W12" s="67" t="n"/>
+      <c r="X12" s="67" t="n"/>
+      <c r="Y12" s="67" t="n"/>
+      <c r="Z12" s="67" t="n"/>
+      <c r="AA12" s="67" t="n"/>
+      <c r="AB12" s="67" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="B13" s="18" t="n">
@@ -1454,6 +1568,13 @@
       </c>
       <c r="T13" s="16" t="n"/>
       <c r="U13" s="17" t="n"/>
+      <c r="V13" s="67" t="n"/>
+      <c r="W13" s="67" t="n"/>
+      <c r="X13" s="67" t="n"/>
+      <c r="Y13" s="67" t="n"/>
+      <c r="Z13" s="67" t="n"/>
+      <c r="AA13" s="67" t="n"/>
+      <c r="AB13" s="67" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="B14" s="8" t="n">
@@ -1520,6 +1641,13 @@
       </c>
       <c r="T14" s="16" t="n"/>
       <c r="U14" s="17" t="n"/>
+      <c r="V14" s="67" t="n"/>
+      <c r="W14" s="67" t="n"/>
+      <c r="X14" s="67" t="n"/>
+      <c r="Y14" s="67" t="n"/>
+      <c r="Z14" s="67" t="n"/>
+      <c r="AA14" s="67" t="n"/>
+      <c r="AB14" s="67" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="18" t="n">
@@ -1585,6 +1713,13 @@
       </c>
       <c r="T15" s="16" t="n"/>
       <c r="U15" s="17" t="n"/>
+      <c r="V15" s="67" t="n"/>
+      <c r="W15" s="67" t="n"/>
+      <c r="X15" s="67" t="n"/>
+      <c r="Y15" s="67" t="n"/>
+      <c r="Z15" s="67" t="n"/>
+      <c r="AA15" s="67" t="n"/>
+      <c r="AB15" s="67" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="8" t="n">
@@ -1652,6 +1787,13 @@
       </c>
       <c r="T16" s="16" t="n"/>
       <c r="U16" s="17" t="n"/>
+      <c r="V16" s="67" t="n"/>
+      <c r="W16" s="67" t="n"/>
+      <c r="X16" s="67" t="n"/>
+      <c r="Y16" s="67" t="n"/>
+      <c r="Z16" s="67" t="n"/>
+      <c r="AA16" s="67" t="n"/>
+      <c r="AB16" s="67" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="18" t="n">
@@ -1717,6 +1859,13 @@
       </c>
       <c r="T17" s="16" t="n"/>
       <c r="U17" s="17" t="n"/>
+      <c r="V17" s="67" t="n"/>
+      <c r="W17" s="67" t="n"/>
+      <c r="X17" s="67" t="n"/>
+      <c r="Y17" s="67" t="n"/>
+      <c r="Z17" s="67" t="n"/>
+      <c r="AA17" s="67" t="n"/>
+      <c r="AB17" s="67" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="8" t="n">
@@ -1782,6 +1931,13 @@
       </c>
       <c r="T18" s="16" t="n"/>
       <c r="U18" s="17" t="n"/>
+      <c r="V18" s="67" t="n"/>
+      <c r="W18" s="67" t="n"/>
+      <c r="X18" s="67" t="n"/>
+      <c r="Y18" s="67" t="n"/>
+      <c r="Z18" s="67" t="n"/>
+      <c r="AA18" s="67" t="n"/>
+      <c r="AB18" s="67" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="B19" s="18" t="n">
@@ -1847,6 +2003,13 @@
       </c>
       <c r="T19" s="16" t="n"/>
       <c r="U19" s="17" t="n"/>
+      <c r="V19" s="67" t="n"/>
+      <c r="W19" s="67" t="n"/>
+      <c r="X19" s="67" t="n"/>
+      <c r="Y19" s="67" t="n"/>
+      <c r="Z19" s="67" t="n"/>
+      <c r="AA19" s="67" t="n"/>
+      <c r="AB19" s="67" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="B20" s="8" t="n">
@@ -1912,6 +2075,13 @@
       </c>
       <c r="T20" s="16" t="n"/>
       <c r="U20" s="17" t="n"/>
+      <c r="V20" s="67" t="n"/>
+      <c r="W20" s="67" t="n"/>
+      <c r="X20" s="67" t="n"/>
+      <c r="Y20" s="67" t="n"/>
+      <c r="Z20" s="67" t="n"/>
+      <c r="AA20" s="67" t="n"/>
+      <c r="AB20" s="67" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="B21" s="18" t="n">
@@ -1977,6 +2147,13 @@
       </c>
       <c r="T21" s="16" t="n"/>
       <c r="U21" s="17" t="n"/>
+      <c r="V21" s="67" t="n"/>
+      <c r="W21" s="67" t="n"/>
+      <c r="X21" s="67" t="n"/>
+      <c r="Y21" s="67" t="n"/>
+      <c r="Z21" s="67" t="n"/>
+      <c r="AA21" s="67" t="n"/>
+      <c r="AB21" s="67" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="B22" s="8" t="n">
@@ -2042,6 +2219,13 @@
       </c>
       <c r="T22" s="16" t="n"/>
       <c r="U22" s="17" t="n"/>
+      <c r="V22" s="67" t="n"/>
+      <c r="W22" s="67" t="n"/>
+      <c r="X22" s="67" t="n"/>
+      <c r="Y22" s="67" t="n"/>
+      <c r="Z22" s="67" t="n"/>
+      <c r="AA22" s="67" t="n"/>
+      <c r="AB22" s="67" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="18" t="n">
@@ -2103,6 +2287,13 @@
       </c>
       <c r="T23" s="16" t="n"/>
       <c r="U23" s="17" t="n"/>
+      <c r="V23" s="67" t="n"/>
+      <c r="W23" s="67" t="n"/>
+      <c r="X23" s="67" t="n"/>
+      <c r="Y23" s="67" t="n"/>
+      <c r="Z23" s="67" t="n"/>
+      <c r="AA23" s="67" t="n"/>
+      <c r="AB23" s="67" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="8" t="n">
@@ -2168,6 +2359,13 @@
       </c>
       <c r="T24" s="16" t="n"/>
       <c r="U24" s="17" t="n"/>
+      <c r="V24" s="67" t="n"/>
+      <c r="W24" s="67" t="n"/>
+      <c r="X24" s="67" t="n"/>
+      <c r="Y24" s="67" t="n"/>
+      <c r="Z24" s="67" t="n"/>
+      <c r="AA24" s="67" t="n"/>
+      <c r="AB24" s="67" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="B25" s="18" t="n">
@@ -2235,6 +2433,13 @@
       </c>
       <c r="T25" s="16" t="n"/>
       <c r="U25" s="17" t="n"/>
+      <c r="V25" s="67" t="n"/>
+      <c r="W25" s="67" t="n"/>
+      <c r="X25" s="67" t="n"/>
+      <c r="Y25" s="67" t="n"/>
+      <c r="Z25" s="67" t="n"/>
+      <c r="AA25" s="67" t="n"/>
+      <c r="AB25" s="67" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="8" t="n">
@@ -2300,6 +2505,13 @@
       </c>
       <c r="T26" s="16" t="n"/>
       <c r="U26" s="17" t="n"/>
+      <c r="V26" s="67" t="n"/>
+      <c r="W26" s="67" t="n"/>
+      <c r="X26" s="67" t="n"/>
+      <c r="Y26" s="67" t="n"/>
+      <c r="Z26" s="67" t="n"/>
+      <c r="AA26" s="67" t="n"/>
+      <c r="AB26" s="67" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="B27" s="18" t="n">
@@ -2366,6 +2578,13 @@
       </c>
       <c r="T27" s="16" t="n"/>
       <c r="U27" s="17" t="n"/>
+      <c r="V27" s="67" t="n"/>
+      <c r="W27" s="67" t="n"/>
+      <c r="X27" s="67" t="n"/>
+      <c r="Y27" s="67" t="n"/>
+      <c r="Z27" s="67" t="n"/>
+      <c r="AA27" s="67" t="n"/>
+      <c r="AB27" s="67" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="8" t="n">
@@ -2432,6 +2651,13 @@
       </c>
       <c r="T28" s="16" t="n"/>
       <c r="U28" s="17" t="n"/>
+      <c r="V28" s="67" t="n"/>
+      <c r="W28" s="67" t="n"/>
+      <c r="X28" s="67" t="n"/>
+      <c r="Y28" s="67" t="n"/>
+      <c r="Z28" s="67" t="n"/>
+      <c r="AA28" s="67" t="n"/>
+      <c r="AB28" s="67" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="18" t="n">
@@ -2497,6 +2723,13 @@
       </c>
       <c r="T29" s="16" t="n"/>
       <c r="U29" s="17" t="n"/>
+      <c r="V29" s="67" t="n"/>
+      <c r="W29" s="67" t="n"/>
+      <c r="X29" s="67" t="n"/>
+      <c r="Y29" s="67" t="n"/>
+      <c r="Z29" s="67" t="n"/>
+      <c r="AA29" s="67" t="n"/>
+      <c r="AB29" s="67" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="B30" s="8" t="n">
@@ -2562,6 +2795,13 @@
       </c>
       <c r="T30" s="16" t="n"/>
       <c r="U30" s="17" t="n"/>
+      <c r="V30" s="67" t="n"/>
+      <c r="W30" s="67" t="n"/>
+      <c r="X30" s="67" t="n"/>
+      <c r="Y30" s="67" t="n"/>
+      <c r="Z30" s="67" t="n"/>
+      <c r="AA30" s="67" t="n"/>
+      <c r="AB30" s="67" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="18" t="n">
@@ -2628,6 +2868,13 @@
       </c>
       <c r="T31" s="16" t="n"/>
       <c r="U31" s="17" t="n"/>
+      <c r="V31" s="67" t="n"/>
+      <c r="W31" s="67" t="n"/>
+      <c r="X31" s="67" t="n"/>
+      <c r="Y31" s="67" t="n"/>
+      <c r="Z31" s="67" t="n"/>
+      <c r="AA31" s="67" t="n"/>
+      <c r="AB31" s="67" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="8" t="n">
@@ -2693,6 +2940,13 @@
       </c>
       <c r="T32" s="16" t="n"/>
       <c r="U32" s="17" t="n"/>
+      <c r="V32" s="67" t="n"/>
+      <c r="W32" s="67" t="n"/>
+      <c r="X32" s="67" t="n"/>
+      <c r="Y32" s="67" t="n"/>
+      <c r="Z32" s="67" t="n"/>
+      <c r="AA32" s="67" t="n"/>
+      <c r="AB32" s="67" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="B33" s="18" t="n">
@@ -2758,6 +3012,13 @@
       </c>
       <c r="T33" s="16" t="n"/>
       <c r="U33" s="17" t="n"/>
+      <c r="V33" s="67" t="n"/>
+      <c r="W33" s="67" t="n"/>
+      <c r="X33" s="67" t="n"/>
+      <c r="Y33" s="67" t="n"/>
+      <c r="Z33" s="67" t="n"/>
+      <c r="AA33" s="67" t="n"/>
+      <c r="AB33" s="67" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="B34" s="8" t="n">
@@ -2823,6 +3084,13 @@
       </c>
       <c r="T34" s="16" t="n"/>
       <c r="U34" s="17" t="n"/>
+      <c r="V34" s="67" t="n"/>
+      <c r="W34" s="67" t="n"/>
+      <c r="X34" s="67" t="n"/>
+      <c r="Y34" s="67" t="n"/>
+      <c r="Z34" s="67" t="n"/>
+      <c r="AA34" s="67" t="n"/>
+      <c r="AB34" s="67" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="B35" s="18" t="n">
@@ -2890,6 +3158,13 @@
       </c>
       <c r="T35" s="16" t="n"/>
       <c r="U35" s="17" t="n"/>
+      <c r="V35" s="67" t="n"/>
+      <c r="W35" s="67" t="n"/>
+      <c r="X35" s="67" t="n"/>
+      <c r="Y35" s="67" t="n"/>
+      <c r="Z35" s="67" t="n"/>
+      <c r="AA35" s="67" t="n"/>
+      <c r="AB35" s="67" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="8" t="n">
@@ -2955,6 +3230,13 @@
       </c>
       <c r="T36" s="16" t="n"/>
       <c r="U36" s="17" t="n"/>
+      <c r="V36" s="67" t="n"/>
+      <c r="W36" s="67" t="n"/>
+      <c r="X36" s="67" t="n"/>
+      <c r="Y36" s="67" t="n"/>
+      <c r="Z36" s="67" t="n"/>
+      <c r="AA36" s="67" t="n"/>
+      <c r="AB36" s="67" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="18" t="n">
@@ -3020,6 +3302,13 @@
       </c>
       <c r="T37" s="16" t="n"/>
       <c r="U37" s="17" t="n"/>
+      <c r="V37" s="67" t="n"/>
+      <c r="W37" s="67" t="n"/>
+      <c r="X37" s="67" t="n"/>
+      <c r="Y37" s="67" t="n"/>
+      <c r="Z37" s="67" t="n"/>
+      <c r="AA37" s="67" t="n"/>
+      <c r="AB37" s="67" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="B38" s="8" t="n">
@@ -3086,6 +3375,13 @@
       </c>
       <c r="T38" s="16" t="n"/>
       <c r="U38" s="17" t="n"/>
+      <c r="V38" s="67" t="n"/>
+      <c r="W38" s="67" t="n"/>
+      <c r="X38" s="67" t="n"/>
+      <c r="Y38" s="67" t="n"/>
+      <c r="Z38" s="67" t="n"/>
+      <c r="AA38" s="67" t="n"/>
+      <c r="AB38" s="67" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="B39" s="18" t="n">
@@ -3152,6 +3448,13 @@
       </c>
       <c r="T39" s="16" t="n"/>
       <c r="U39" s="17" t="n"/>
+      <c r="V39" s="67" t="n"/>
+      <c r="W39" s="67" t="n"/>
+      <c r="X39" s="67" t="n"/>
+      <c r="Y39" s="67" t="n"/>
+      <c r="Z39" s="67" t="n"/>
+      <c r="AA39" s="67" t="n"/>
+      <c r="AB39" s="67" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="B40" s="8" t="n">
@@ -3217,6 +3520,13 @@
       </c>
       <c r="T40" s="16" t="n"/>
       <c r="U40" s="17" t="n"/>
+      <c r="V40" s="67" t="n"/>
+      <c r="W40" s="67" t="n"/>
+      <c r="X40" s="67" t="n"/>
+      <c r="Y40" s="67" t="n"/>
+      <c r="Z40" s="67" t="n"/>
+      <c r="AA40" s="67" t="n"/>
+      <c r="AB40" s="67" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="B41" s="18" t="n">
@@ -3282,6 +3592,13 @@
       </c>
       <c r="T41" s="16" t="n"/>
       <c r="U41" s="17" t="n"/>
+      <c r="V41" s="67" t="n"/>
+      <c r="W41" s="67" t="n"/>
+      <c r="X41" s="67" t="n"/>
+      <c r="Y41" s="67" t="n"/>
+      <c r="Z41" s="67" t="n"/>
+      <c r="AA41" s="67" t="n"/>
+      <c r="AB41" s="67" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="B42" s="8" t="n">
@@ -3347,6 +3664,13 @@
       </c>
       <c r="T42" s="16" t="n"/>
       <c r="U42" s="17" t="n"/>
+      <c r="V42" s="67" t="n"/>
+      <c r="W42" s="67" t="n"/>
+      <c r="X42" s="67" t="n"/>
+      <c r="Y42" s="67" t="n"/>
+      <c r="Z42" s="67" t="n"/>
+      <c r="AA42" s="67" t="n"/>
+      <c r="AB42" s="67" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="B43" s="18" t="n">
@@ -3412,6 +3736,13 @@
       </c>
       <c r="T43" s="16" t="n"/>
       <c r="U43" s="17" t="n"/>
+      <c r="V43" s="67" t="n"/>
+      <c r="W43" s="67" t="n"/>
+      <c r="X43" s="67" t="n"/>
+      <c r="Y43" s="67" t="n"/>
+      <c r="Z43" s="67" t="n"/>
+      <c r="AA43" s="67" t="n"/>
+      <c r="AB43" s="67" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="B44" s="8" t="n">
@@ -3473,6 +3804,13 @@
       </c>
       <c r="T44" s="16" t="n"/>
       <c r="U44" s="17" t="n"/>
+      <c r="V44" s="67" t="n"/>
+      <c r="W44" s="67" t="n"/>
+      <c r="X44" s="67" t="n"/>
+      <c r="Y44" s="67" t="n"/>
+      <c r="Z44" s="67" t="n"/>
+      <c r="AA44" s="67" t="n"/>
+      <c r="AB44" s="67" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="B45" s="18" t="n">
@@ -3534,6 +3872,13 @@
       </c>
       <c r="T45" s="16" t="n"/>
       <c r="U45" s="17" t="n"/>
+      <c r="V45" s="67" t="n"/>
+      <c r="W45" s="67" t="n"/>
+      <c r="X45" s="67" t="n"/>
+      <c r="Y45" s="67" t="n"/>
+      <c r="Z45" s="67" t="n"/>
+      <c r="AA45" s="67" t="n"/>
+      <c r="AB45" s="67" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="B46" s="8" t="n">
@@ -3595,6 +3940,13 @@
       </c>
       <c r="T46" s="16" t="n"/>
       <c r="U46" s="17" t="n"/>
+      <c r="V46" s="67" t="n"/>
+      <c r="W46" s="67" t="n"/>
+      <c r="X46" s="67" t="n"/>
+      <c r="Y46" s="67" t="n"/>
+      <c r="Z46" s="67" t="n"/>
+      <c r="AA46" s="67" t="n"/>
+      <c r="AB46" s="67" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="B47" s="18" t="n">
@@ -3660,6 +4012,13 @@
       </c>
       <c r="T47" s="16" t="n"/>
       <c r="U47" s="17" t="n"/>
+      <c r="V47" s="67" t="n"/>
+      <c r="W47" s="67" t="n"/>
+      <c r="X47" s="67" t="n"/>
+      <c r="Y47" s="67" t="n"/>
+      <c r="Z47" s="67" t="n"/>
+      <c r="AA47" s="67" t="n"/>
+      <c r="AB47" s="67" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="B48" s="8" t="n">
@@ -3728,6 +4087,13 @@
       </c>
       <c r="T48" s="16" t="n"/>
       <c r="U48" s="17" t="n"/>
+      <c r="V48" s="67" t="n"/>
+      <c r="W48" s="67" t="n"/>
+      <c r="X48" s="67" t="n"/>
+      <c r="Y48" s="67" t="n"/>
+      <c r="Z48" s="67" t="n"/>
+      <c r="AA48" s="67" t="n"/>
+      <c r="AB48" s="67" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="B49" s="18" t="n">
@@ -3793,6 +4159,13 @@
       </c>
       <c r="T49" s="16" t="n"/>
       <c r="U49" s="17" t="n"/>
+      <c r="V49" s="67" t="n"/>
+      <c r="W49" s="67" t="n"/>
+      <c r="X49" s="67" t="n"/>
+      <c r="Y49" s="67" t="n"/>
+      <c r="Z49" s="67" t="n"/>
+      <c r="AA49" s="67" t="n"/>
+      <c r="AB49" s="67" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="B50" s="8" t="n">
@@ -3858,6 +4231,13 @@
       </c>
       <c r="T50" s="16" t="n"/>
       <c r="U50" s="17" t="n"/>
+      <c r="V50" s="67" t="n"/>
+      <c r="W50" s="67" t="n"/>
+      <c r="X50" s="67" t="n"/>
+      <c r="Y50" s="67" t="n"/>
+      <c r="Z50" s="67" t="n"/>
+      <c r="AA50" s="67" t="n"/>
+      <c r="AB50" s="67" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="B51" s="18" t="n">
@@ -3923,6 +4303,13 @@
       </c>
       <c r="T51" s="16" t="n"/>
       <c r="U51" s="17" t="n"/>
+      <c r="V51" s="67" t="n"/>
+      <c r="W51" s="67" t="n"/>
+      <c r="X51" s="67" t="n"/>
+      <c r="Y51" s="67" t="n"/>
+      <c r="Z51" s="67" t="n"/>
+      <c r="AA51" s="67" t="n"/>
+      <c r="AB51" s="67" t="n"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="B52" s="8" t="n">
@@ -3988,6 +4375,13 @@
       </c>
       <c r="T52" s="16" t="n"/>
       <c r="U52" s="17" t="n"/>
+      <c r="V52" s="67" t="n"/>
+      <c r="W52" s="67" t="n"/>
+      <c r="X52" s="67" t="n"/>
+      <c r="Y52" s="67" t="n"/>
+      <c r="Z52" s="67" t="n"/>
+      <c r="AA52" s="67" t="n"/>
+      <c r="AB52" s="67" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="B53" s="18" t="n">
@@ -4049,6 +4443,13 @@
       </c>
       <c r="T53" s="16" t="n"/>
       <c r="U53" s="17" t="n"/>
+      <c r="V53" s="67" t="n"/>
+      <c r="W53" s="67" t="n"/>
+      <c r="X53" s="67" t="n"/>
+      <c r="Y53" s="67" t="n"/>
+      <c r="Z53" s="67" t="n"/>
+      <c r="AA53" s="67" t="n"/>
+      <c r="AB53" s="67" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="8" t="n">
@@ -4110,6 +4511,13 @@
       </c>
       <c r="T54" s="16" t="n"/>
       <c r="U54" s="17" t="n"/>
+      <c r="V54" s="67" t="n"/>
+      <c r="W54" s="67" t="n"/>
+      <c r="X54" s="67" t="n"/>
+      <c r="Y54" s="67" t="n"/>
+      <c r="Z54" s="67" t="n"/>
+      <c r="AA54" s="67" t="n"/>
+      <c r="AB54" s="67" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="B55" s="18" t="n">
@@ -4175,6 +4583,13 @@
       </c>
       <c r="T55" s="16" t="n"/>
       <c r="U55" s="17" t="n"/>
+      <c r="V55" s="67" t="n"/>
+      <c r="W55" s="67" t="n"/>
+      <c r="X55" s="67" t="n"/>
+      <c r="Y55" s="67" t="n"/>
+      <c r="Z55" s="67" t="n"/>
+      <c r="AA55" s="67" t="n"/>
+      <c r="AB55" s="67" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="8" t="n">
@@ -4240,6 +4655,13 @@
       </c>
       <c r="T56" s="16" t="n"/>
       <c r="U56" s="17" t="n"/>
+      <c r="V56" s="67" t="n"/>
+      <c r="W56" s="67" t="n"/>
+      <c r="X56" s="67" t="n"/>
+      <c r="Y56" s="67" t="n"/>
+      <c r="Z56" s="67" t="n"/>
+      <c r="AA56" s="67" t="n"/>
+      <c r="AB56" s="67" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="18" t="n">
@@ -4305,6 +4727,13 @@
       </c>
       <c r="T57" s="16" t="n"/>
       <c r="U57" s="17" t="n"/>
+      <c r="V57" s="67" t="n"/>
+      <c r="W57" s="67" t="n"/>
+      <c r="X57" s="67" t="n"/>
+      <c r="Y57" s="67" t="n"/>
+      <c r="Z57" s="67" t="n"/>
+      <c r="AA57" s="67" t="n"/>
+      <c r="AB57" s="67" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="8" t="n">
@@ -4370,6 +4799,13 @@
       </c>
       <c r="T58" s="16" t="n"/>
       <c r="U58" s="17" t="n"/>
+      <c r="V58" s="67" t="n"/>
+      <c r="W58" s="67" t="n"/>
+      <c r="X58" s="67" t="n"/>
+      <c r="Y58" s="67" t="n"/>
+      <c r="Z58" s="67" t="n"/>
+      <c r="AA58" s="67" t="n"/>
+      <c r="AB58" s="67" t="n"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="18" t="n">
@@ -4435,6 +4871,13 @@
       </c>
       <c r="T59" s="16" t="n"/>
       <c r="U59" s="17" t="n"/>
+      <c r="V59" s="67" t="n"/>
+      <c r="W59" s="67" t="n"/>
+      <c r="X59" s="67" t="n"/>
+      <c r="Y59" s="67" t="n"/>
+      <c r="Z59" s="67" t="n"/>
+      <c r="AA59" s="67" t="n"/>
+      <c r="AB59" s="67" t="n"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="8" t="n">
@@ -4500,6 +4943,13 @@
       </c>
       <c r="T60" s="16" t="n"/>
       <c r="U60" s="17" t="n"/>
+      <c r="V60" s="67" t="n"/>
+      <c r="W60" s="67" t="n"/>
+      <c r="X60" s="67" t="n"/>
+      <c r="Y60" s="67" t="n"/>
+      <c r="Z60" s="67" t="n"/>
+      <c r="AA60" s="67" t="n"/>
+      <c r="AB60" s="67" t="n"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="18" t="n">
@@ -4565,6 +5015,13 @@
       </c>
       <c r="T61" s="16" t="n"/>
       <c r="U61" s="17" t="n"/>
+      <c r="V61" s="67" t="n"/>
+      <c r="W61" s="67" t="n"/>
+      <c r="X61" s="67" t="n"/>
+      <c r="Y61" s="67" t="n"/>
+      <c r="Z61" s="67" t="n"/>
+      <c r="AA61" s="67" t="n"/>
+      <c r="AB61" s="67" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="8" t="n">
@@ -4630,6 +5087,13 @@
       </c>
       <c r="T62" s="16" t="n"/>
       <c r="U62" s="17" t="n"/>
+      <c r="V62" s="67" t="n"/>
+      <c r="W62" s="67" t="n"/>
+      <c r="X62" s="67" t="n"/>
+      <c r="Y62" s="67" t="n"/>
+      <c r="Z62" s="67" t="n"/>
+      <c r="AA62" s="67" t="n"/>
+      <c r="AB62" s="67" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="18" t="n">
@@ -4695,6 +5159,13 @@
       </c>
       <c r="T63" s="16" t="n"/>
       <c r="U63" s="17" t="n"/>
+      <c r="V63" s="67" t="n"/>
+      <c r="W63" s="67" t="n"/>
+      <c r="X63" s="67" t="n"/>
+      <c r="Y63" s="67" t="n"/>
+      <c r="Z63" s="67" t="n"/>
+      <c r="AA63" s="67" t="n"/>
+      <c r="AB63" s="67" t="n"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="8" t="n">
@@ -4760,6 +5231,13 @@
       </c>
       <c r="T64" s="16" t="n"/>
       <c r="U64" s="17" t="n"/>
+      <c r="V64" s="67" t="n"/>
+      <c r="W64" s="67" t="n"/>
+      <c r="X64" s="67" t="n"/>
+      <c r="Y64" s="67" t="n"/>
+      <c r="Z64" s="67" t="n"/>
+      <c r="AA64" s="67" t="n"/>
+      <c r="AB64" s="67" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="18" t="n">
@@ -4825,6 +5303,13 @@
       </c>
       <c r="T65" s="16" t="n"/>
       <c r="U65" s="17" t="n"/>
+      <c r="V65" s="67" t="n"/>
+      <c r="W65" s="67" t="n"/>
+      <c r="X65" s="67" t="n"/>
+      <c r="Y65" s="67" t="n"/>
+      <c r="Z65" s="67" t="n"/>
+      <c r="AA65" s="67" t="n"/>
+      <c r="AB65" s="67" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="8" t="n">
@@ -4890,6 +5375,13 @@
       </c>
       <c r="T66" s="16" t="n"/>
       <c r="U66" s="17" t="n"/>
+      <c r="V66" s="67" t="n"/>
+      <c r="W66" s="67" t="n"/>
+      <c r="X66" s="67" t="n"/>
+      <c r="Y66" s="67" t="n"/>
+      <c r="Z66" s="67" t="n"/>
+      <c r="AA66" s="67" t="n"/>
+      <c r="AB66" s="67" t="n"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="18" t="n">
@@ -4955,6 +5447,13 @@
       </c>
       <c r="T67" s="16" t="n"/>
       <c r="U67" s="17" t="n"/>
+      <c r="V67" s="67" t="n"/>
+      <c r="W67" s="67" t="n"/>
+      <c r="X67" s="67" t="n"/>
+      <c r="Y67" s="67" t="n"/>
+      <c r="Z67" s="67" t="n"/>
+      <c r="AA67" s="67" t="n"/>
+      <c r="AB67" s="67" t="n"/>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="8" t="n">
@@ -5020,6 +5519,13 @@
       </c>
       <c r="T68" s="16" t="n"/>
       <c r="U68" s="17" t="n"/>
+      <c r="V68" s="67" t="n"/>
+      <c r="W68" s="67" t="n"/>
+      <c r="X68" s="67" t="n"/>
+      <c r="Y68" s="67" t="n"/>
+      <c r="Z68" s="67" t="n"/>
+      <c r="AA68" s="67" t="n"/>
+      <c r="AB68" s="67" t="n"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="18" t="n">
@@ -5085,6 +5591,13 @@
       </c>
       <c r="T69" s="16" t="n"/>
       <c r="U69" s="17" t="n"/>
+      <c r="V69" s="67" t="n"/>
+      <c r="W69" s="67" t="n"/>
+      <c r="X69" s="67" t="n"/>
+      <c r="Y69" s="67" t="n"/>
+      <c r="Z69" s="67" t="n"/>
+      <c r="AA69" s="67" t="n"/>
+      <c r="AB69" s="67" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="8" t="n">
@@ -5150,6 +5663,13 @@
       </c>
       <c r="T70" s="16" t="n"/>
       <c r="U70" s="17" t="n"/>
+      <c r="V70" s="67" t="n"/>
+      <c r="W70" s="67" t="n"/>
+      <c r="X70" s="67" t="n"/>
+      <c r="Y70" s="67" t="n"/>
+      <c r="Z70" s="67" t="n"/>
+      <c r="AA70" s="67" t="n"/>
+      <c r="AB70" s="67" t="n"/>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="18" t="n">
@@ -5215,6 +5735,13 @@
       </c>
       <c r="T71" s="16" t="n"/>
       <c r="U71" s="17" t="n"/>
+      <c r="V71" s="67" t="n"/>
+      <c r="W71" s="67" t="n"/>
+      <c r="X71" s="67" t="n"/>
+      <c r="Y71" s="67" t="n"/>
+      <c r="Z71" s="67" t="n"/>
+      <c r="AA71" s="67" t="n"/>
+      <c r="AB71" s="67" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="8" t="n">
@@ -5280,6 +5807,13 @@
       </c>
       <c r="T72" s="16" t="n"/>
       <c r="U72" s="17" t="n"/>
+      <c r="V72" s="67" t="n"/>
+      <c r="W72" s="67" t="n"/>
+      <c r="X72" s="67" t="n"/>
+      <c r="Y72" s="67" t="n"/>
+      <c r="Z72" s="67" t="n"/>
+      <c r="AA72" s="67" t="n"/>
+      <c r="AB72" s="67" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="18" t="n">
@@ -5345,6 +5879,13 @@
       </c>
       <c r="T73" s="16" t="n"/>
       <c r="U73" s="17" t="n"/>
+      <c r="V73" s="67" t="n"/>
+      <c r="W73" s="67" t="n"/>
+      <c r="X73" s="67" t="n"/>
+      <c r="Y73" s="67" t="n"/>
+      <c r="Z73" s="67" t="n"/>
+      <c r="AA73" s="67" t="n"/>
+      <c r="AB73" s="67" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="8" t="n">
@@ -5410,6 +5951,13 @@
       </c>
       <c r="T74" s="16" t="n"/>
       <c r="U74" s="17" t="n"/>
+      <c r="V74" s="67" t="n"/>
+      <c r="W74" s="67" t="n"/>
+      <c r="X74" s="67" t="n"/>
+      <c r="Y74" s="67" t="n"/>
+      <c r="Z74" s="67" t="n"/>
+      <c r="AA74" s="67" t="n"/>
+      <c r="AB74" s="67" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="B75" s="18" t="n">
@@ -5475,6 +6023,13 @@
       </c>
       <c r="T75" s="16" t="n"/>
       <c r="U75" s="17" t="n"/>
+      <c r="V75" s="67" t="n"/>
+      <c r="W75" s="67" t="n"/>
+      <c r="X75" s="67" t="n"/>
+      <c r="Y75" s="67" t="n"/>
+      <c r="Z75" s="67" t="n"/>
+      <c r="AA75" s="67" t="n"/>
+      <c r="AB75" s="67" t="n"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="8" t="n">
@@ -5548,6 +6103,13 @@
       </c>
       <c r="T76" s="16" t="n"/>
       <c r="U76" s="17" t="n"/>
+      <c r="V76" s="67" t="n"/>
+      <c r="W76" s="67" t="n"/>
+      <c r="X76" s="67" t="n"/>
+      <c r="Y76" s="67" t="n"/>
+      <c r="Z76" s="67" t="n"/>
+      <c r="AA76" s="67" t="n"/>
+      <c r="AB76" s="67" t="n"/>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="B77" s="18" t="n">
@@ -5613,6 +6175,13 @@
       </c>
       <c r="T77" s="16" t="n"/>
       <c r="U77" s="17" t="n"/>
+      <c r="V77" s="67" t="n"/>
+      <c r="W77" s="67" t="n"/>
+      <c r="X77" s="67" t="n"/>
+      <c r="Y77" s="67" t="n"/>
+      <c r="Z77" s="67" t="n"/>
+      <c r="AA77" s="67" t="n"/>
+      <c r="AB77" s="67" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="24" t="inlineStr">
@@ -7155,7 +7724,7 @@
       </c>
       <c r="C20" s="62" t="inlineStr">
         <is>
-          <t>Recopier les valeurs de 'Sem. Act.' de la semaine précédente dans les colonnes 'Sem. Préc.' (J et M)</t>
+          <t>Recopier les valeurs de 'Sem. Act.' de la semaine précédente dans les colonnes + 7 colonnes consultation 'Sem. Préc.' (J et M)</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7736,7 @@
       </c>
       <c r="C21" s="62" t="inlineStr">
         <is>
-          <t>Saisir les nouvelles valeurs d'avancement physique et financier dans les colonnes 'Sem. Act.' (K et N)</t>
+          <t>Saisir les nouvelles valeurs d'avancement physique et financier dans les colonnes + 7 colonnes consultation 'Sem. Act.' (K et N)</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7799,7 @@
     <row r="28">
       <c r="C28" s="62" t="inlineStr">
         <is>
-          <t>• Ne jamais modifier les colonnes calculées (formules) — elles se mettent à jour automatiquement
+          <t>• Ne jamais modifier les colonnes + 7 colonnes consultation calculées (formules) — elles se mettent à jour automatiquement
 • Toujours sauvegarder une copie hebdomadaire avant de saisir les nouvelles données
 • Les cases jaunes sont les champs à remplir manuellement
 • Le filtre automatique permet de filtrer par province, commune ou statut</t>
